--- a/survey_templates/014_family_communication_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/014_family_communication_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'0-1_time_in_a_month'}</t>
+          <t>0-1_time_in_a_month</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '0-1 time in a month'}</t>
+          <t>0-1 time in a month</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2-3_times_in_a_month'}</t>
+          <t>2-3_times_in_a_month</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2-3 times in a month'}</t>
+          <t>2-3 times in a month</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'4_or_more_times_in_a_month'}</t>
+          <t>4_or_more_times_in_a_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '4 or more times in a month'}</t>
+          <t>4 or more times in a month</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'cooperative'}</t>
+          <t>cooperative</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Cooperative'}</t>
+          <t>Cooperative</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'competitive'}</t>
+          <t>competitive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Competitive'}</t>
+          <t>Competitive</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'independent'}</t>
+          <t>independent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Independent'}</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'authoritative'}</t>
+          <t>authoritative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Authoritative'}</t>
+          <t>Authoritative</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'collaborative'}</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Collaborative'}</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'avoiding'}</t>
+          <t>avoiding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Avoiding'}</t>
+          <t>Avoiding</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'frustrating'}</t>
+          <t>frustrating</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Frustrating'}</t>
+          <t>Frustrating</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'0-1_time_in_a_month'}</t>
+          <t>0-1_time_in_a_month</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '0-1 time in a month'}</t>
+          <t>0-1 time in a month</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'2-3_times_in_a_month'}</t>
+          <t>2-3_times_in_a_month</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '2-3 times in a month'}</t>
+          <t>2-3 times in a month</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'4_or_more_times_in_a_month'}</t>
+          <t>4_or_more_times_in_a_month</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '4 or more times in a month'}</t>
+          <t>4 or more times in a month</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
